--- a/Base_Limpia.xlsx
+++ b/Base_Limpia.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scalv\OneDrive\Documentos\UCR\Ciclos\V Ciclo\Modelos Lineales Avanzados\Proyecto\Tratamiento_Base\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scalv\OneDrive\Documentos\GitHub\Proyecto-Lineales-avanzados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{440684FA-AE79-4A09-8F47-44DC68B22A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35145388-1722-4514-867B-8B6DC0796EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{832891C7-FD55-44BA-864F-0A91591BDCAB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{832891C7-FD55-44BA-864F-0A91591BDCAB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="51">
   <si>
     <t>id_est</t>
   </si>
@@ -191,12 +191,6 @@
     <t>s24</t>
   </si>
   <si>
-    <t>s26</t>
-  </si>
-  <si>
-    <t>s27</t>
-  </si>
-  <si>
     <t>s28</t>
   </si>
 </sst>
@@ -204,7 +198,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -628,13 +622,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{644890D0-F483-4F00-BD2C-9D89F57C5364}">
-  <dimension ref="A1:J157"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <dimension ref="A1:J149"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -666,7 +660,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -683,7 +677,7 @@
         <v>0.42430555555555555</v>
       </c>
       <c r="F2" s="3">
-        <f>E2-D2</f>
+        <f t="shared" ref="F2:F33" si="0">E2-D2</f>
         <v>4.2361111111111127E-2</v>
       </c>
       <c r="G2">
@@ -699,7 +693,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -716,7 +710,7 @@
         <v>0.44513888888888886</v>
       </c>
       <c r="F3" s="3">
-        <f>E3-D3</f>
+        <f t="shared" si="0"/>
         <v>8.3333333333333037E-3</v>
       </c>
       <c r="G3">
@@ -732,7 +726,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -749,7 +743,7 @@
         <v>0.47708333333333336</v>
       </c>
       <c r="F4" s="3">
-        <f>E4-D4</f>
+        <f t="shared" si="0"/>
         <v>2.9166666666666674E-2</v>
       </c>
       <c r="G4">
@@ -765,7 +759,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -782,7 +776,7 @@
         <v>0.49305555555555558</v>
       </c>
       <c r="F5" s="3">
-        <f>E5-D5</f>
+        <f t="shared" si="0"/>
         <v>1.3888888888888895E-2</v>
       </c>
       <c r="G5">
@@ -798,7 +792,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -815,7 +809,7 @@
         <v>0.40208333333333335</v>
       </c>
       <c r="F6" s="3">
-        <f>E6-D6</f>
+        <f t="shared" si="0"/>
         <v>1.6666666666666663E-2</v>
       </c>
       <c r="G6">
@@ -831,7 +825,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -848,7 +842,7 @@
         <v>0.44374999999999998</v>
       </c>
       <c r="F7" s="3">
-        <f>E7-D7</f>
+        <f t="shared" si="0"/>
         <v>2.1527777777777757E-2</v>
       </c>
       <c r="G7">
@@ -864,7 +858,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -881,7 +875,7 @@
         <v>0.42083333333333334</v>
       </c>
       <c r="F8" s="3">
-        <f>E8-D8</f>
+        <f t="shared" si="0"/>
         <v>1.3888888888888895E-2</v>
       </c>
       <c r="G8">
@@ -897,7 +891,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -914,7 +908,7 @@
         <v>0.45624999999999999</v>
       </c>
       <c r="F9" s="3">
-        <f>E9-D9</f>
+        <f t="shared" si="0"/>
         <v>1.041666666666663E-2</v>
       </c>
       <c r="G9">
@@ -930,7 +924,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -947,7 +941,7 @@
         <v>0.3923611111111111</v>
       </c>
       <c r="F10" s="3">
-        <f>E10-D10</f>
+        <f t="shared" si="0"/>
         <v>8.3333333333333037E-3</v>
       </c>
       <c r="G10">
@@ -963,7 +957,7 @@
         <v>92.5</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
@@ -980,7 +974,7 @@
         <v>0.41249999999999998</v>
       </c>
       <c r="F11" s="3">
-        <f>E11-D11</f>
+        <f t="shared" si="0"/>
         <v>1.1805555555555514E-2</v>
       </c>
       <c r="G11">
@@ -996,7 +990,7 @@
         <v>77.5</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -1013,7 +1007,7 @@
         <v>0.43055555555555558</v>
       </c>
       <c r="F12" s="3">
-        <f>E12-D12</f>
+        <f t="shared" si="0"/>
         <v>1.0416666666666685E-2</v>
       </c>
       <c r="G12">
@@ -1029,7 +1023,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
@@ -1046,7 +1040,7 @@
         <v>0.46736111111111112</v>
       </c>
       <c r="F13" s="3">
-        <f>E13-D13</f>
+        <f t="shared" si="0"/>
         <v>2.1527777777777757E-2</v>
       </c>
       <c r="G13">
@@ -1062,7 +1056,7 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>16</v>
       </c>
@@ -1079,7 +1073,7 @@
         <v>0.40972222222222221</v>
       </c>
       <c r="F14" s="3">
-        <f>E14-D14</f>
+        <f t="shared" si="0"/>
         <v>1.9444444444444431E-2</v>
       </c>
       <c r="G14">
@@ -1095,7 +1089,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
@@ -1112,7 +1106,7 @@
         <v>0.47152777777777777</v>
       </c>
       <c r="F15" s="3">
-        <f>E15-D15</f>
+        <f t="shared" si="0"/>
         <v>6.2499999999999778E-3</v>
       </c>
       <c r="G15">
@@ -1128,7 +1122,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
@@ -1145,7 +1139,7 @@
         <v>0.44097222222222221</v>
       </c>
       <c r="F16" s="3">
-        <f>E16-D16</f>
+        <f t="shared" si="0"/>
         <v>2.6388888888888851E-2</v>
       </c>
       <c r="G16">
@@ -1161,7 +1155,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -1178,7 +1172,7 @@
         <v>0.46527777777777779</v>
       </c>
       <c r="F17" s="3">
-        <f>E17-D17</f>
+        <f t="shared" si="0"/>
         <v>2.1527777777777812E-2</v>
       </c>
       <c r="G17">
@@ -1194,7 +1188,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -1211,7 +1205,7 @@
         <v>0.40069444444444446</v>
       </c>
       <c r="F18" s="3">
-        <f>E18-D18</f>
+        <f t="shared" si="0"/>
         <v>1.0416666666666685E-2</v>
       </c>
       <c r="G18">
@@ -1227,7 +1221,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -1244,7 +1238,7 @@
         <v>0.41180555555555554</v>
       </c>
       <c r="F19" s="3">
-        <f>E19-D19</f>
+        <f t="shared" si="0"/>
         <v>9.0277777777777457E-3</v>
       </c>
       <c r="G19">
@@ -1260,7 +1254,7 @@
         <v>97.5</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>17</v>
       </c>
@@ -1277,7 +1271,7 @@
         <v>0.42777777777777776</v>
       </c>
       <c r="F20" s="3">
-        <f>E20-D20</f>
+        <f t="shared" si="0"/>
         <v>1.3194444444444398E-2</v>
       </c>
       <c r="G20">
@@ -1293,7 +1287,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>17</v>
       </c>
@@ -1310,7 +1304,7 @@
         <v>0.4465277777777778</v>
       </c>
       <c r="F21" s="3">
-        <f>E21-D21</f>
+        <f t="shared" si="0"/>
         <v>1.736111111111116E-2</v>
       </c>
       <c r="G21">
@@ -1326,7 +1320,7 @@
         <v>97.5</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>18</v>
       </c>
@@ -1343,7 +1337,7 @@
         <v>0.40972222222222221</v>
       </c>
       <c r="F22" s="3">
-        <f>E22-D22</f>
+        <f t="shared" si="0"/>
         <v>1.3888888888888895E-2</v>
       </c>
       <c r="G22">
@@ -1359,7 +1353,7 @@
         <v>77.5</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1376,7 +1370,7 @@
         <v>0.4375</v>
       </c>
       <c r="F23" s="3">
-        <f>E23-D23</f>
+        <f t="shared" si="0"/>
         <v>2.430555555555558E-2</v>
       </c>
       <c r="G23">
@@ -1392,7 +1386,7 @@
         <v>92.5</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>18</v>
       </c>
@@ -1409,7 +1403,7 @@
         <v>0.47222222222222221</v>
       </c>
       <c r="F24" s="3">
-        <f>E24-D24</f>
+        <f t="shared" si="0"/>
         <v>2.777777777777779E-2</v>
       </c>
       <c r="G24">
@@ -1425,7 +1419,7 @@
         <v>92.5</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>18</v>
       </c>
@@ -1442,7 +1436,7 @@
         <v>0.49305555555555558</v>
       </c>
       <c r="F25" s="3">
-        <f>E25-D25</f>
+        <f t="shared" si="0"/>
         <v>2.083333333333337E-2</v>
       </c>
       <c r="G25">
@@ -1458,7 +1452,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>19</v>
       </c>
@@ -1475,7 +1469,7 @@
         <v>0.41736111111111113</v>
       </c>
       <c r="F26" s="3">
-        <f>E26-D26</f>
+        <f t="shared" si="0"/>
         <v>2.8472222222222232E-2</v>
       </c>
       <c r="G26">
@@ -1491,7 +1485,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>19</v>
       </c>
@@ -1508,7 +1502,7 @@
         <v>0.4375</v>
       </c>
       <c r="F27" s="3">
-        <f>E27-D27</f>
+        <f t="shared" si="0"/>
         <v>1.8055555555555547E-2</v>
       </c>
       <c r="G27">
@@ -1524,7 +1518,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>19</v>
       </c>
@@ -1541,7 +1535,7 @@
         <v>0.46180555555555558</v>
       </c>
       <c r="F28" s="3">
-        <f>E28-D28</f>
+        <f t="shared" si="0"/>
         <v>2.3611111111111138E-2</v>
       </c>
       <c r="G28">
@@ -1557,7 +1551,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
@@ -1574,7 +1568,7 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="F29" s="3">
-        <f>E29-D29</f>
+        <f t="shared" si="0"/>
         <v>1.6666666666666663E-2</v>
       </c>
       <c r="G29">
@@ -1590,7 +1584,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>20</v>
       </c>
@@ -1607,7 +1601,7 @@
         <v>0.41249999999999998</v>
       </c>
       <c r="F30" s="3">
-        <f>E30-D30</f>
+        <f t="shared" si="0"/>
         <v>2.0138888888888873E-2</v>
       </c>
       <c r="G30">
@@ -1623,7 +1617,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>20</v>
       </c>
@@ -1640,7 +1634,7 @@
         <v>0.46875</v>
       </c>
       <c r="F31" s="3">
-        <f>E31-D31</f>
+        <f t="shared" si="0"/>
         <v>8.3333333333333592E-3</v>
       </c>
       <c r="G31">
@@ -1656,7 +1650,7 @@
         <v>97.5</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>20</v>
       </c>
@@ -1673,7 +1667,7 @@
         <v>0.45277777777777778</v>
       </c>
       <c r="F32" s="3">
-        <f>E32-D32</f>
+        <f t="shared" si="0"/>
         <v>2.9166666666666674E-2</v>
       </c>
       <c r="G32">
@@ -1689,7 +1683,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>20</v>
       </c>
@@ -1706,7 +1700,7 @@
         <v>0.48958333333333331</v>
       </c>
       <c r="F33" s="3">
-        <f>E33-D33</f>
+        <f t="shared" si="0"/>
         <v>1.7361111111111105E-2</v>
       </c>
       <c r="G33">
@@ -1722,7 +1716,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>21</v>
       </c>
@@ -1739,7 +1733,7 @@
         <v>0.57222222222222219</v>
       </c>
       <c r="F34" s="3">
-        <f>E34-D34</f>
+        <f t="shared" ref="F34:F65" si="1">E34-D34</f>
         <v>1.9444444444444375E-2</v>
       </c>
       <c r="G34">
@@ -1755,7 +1749,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>21</v>
       </c>
@@ -1772,7 +1766,7 @@
         <v>0.58819444444444446</v>
       </c>
       <c r="F35" s="3">
-        <f>E35-D35</f>
+        <f t="shared" si="1"/>
         <v>1.1111111111111183E-2</v>
       </c>
       <c r="G35">
@@ -1788,7 +1782,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>21</v>
       </c>
@@ -1805,7 +1799,7 @@
         <v>0.6118055555555556</v>
       </c>
       <c r="F36" s="3">
-        <f>E36-D36</f>
+        <f t="shared" si="1"/>
         <v>2.083333333333337E-2</v>
       </c>
       <c r="G36">
@@ -1821,7 +1815,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>21</v>
       </c>
@@ -1838,7 +1832,7 @@
         <v>0.65486111111111112</v>
       </c>
       <c r="F37" s="3">
-        <f>E37-D37</f>
+        <f t="shared" si="1"/>
         <v>4.0972222222222188E-2</v>
       </c>
       <c r="G37">
@@ -1854,7 +1848,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>22</v>
       </c>
@@ -1871,7 +1865,7 @@
         <v>0.43402777777777779</v>
       </c>
       <c r="F38" s="3">
-        <f>E38-D38</f>
+        <f t="shared" si="1"/>
         <v>9.7222222222222432E-3</v>
       </c>
       <c r="G38">
@@ -1887,7 +1881,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>22</v>
       </c>
@@ -1904,7 +1898,7 @@
         <v>0.45208333333333334</v>
       </c>
       <c r="F39" s="3">
-        <f>E39-D39</f>
+        <f t="shared" si="1"/>
         <v>9.0277777777778012E-3</v>
       </c>
       <c r="G39">
@@ -1920,7 +1914,7 @@
         <v>92.5</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>22</v>
       </c>
@@ -1937,7 +1931,7 @@
         <v>0.46944444444444444</v>
       </c>
       <c r="F40" s="3">
-        <f>E40-D40</f>
+        <f t="shared" si="1"/>
         <v>1.1111111111111127E-2</v>
       </c>
       <c r="G40">
@@ -1953,7 +1947,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>22</v>
       </c>
@@ -1970,7 +1964,7 @@
         <v>0.4861111111111111</v>
       </c>
       <c r="F41" s="3">
-        <f>E41-D41</f>
+        <f t="shared" si="1"/>
         <v>8.3333333333333037E-3</v>
       </c>
       <c r="G41">
@@ -1986,7 +1980,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>23</v>
       </c>
@@ -2003,7 +1997,7 @@
         <v>0.55902777777777779</v>
       </c>
       <c r="F42" s="3">
-        <f>E42-D42</f>
+        <f t="shared" si="1"/>
         <v>1.1805555555555514E-2</v>
       </c>
       <c r="G42">
@@ -2019,7 +2013,7 @@
         <v>97.5</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>23</v>
       </c>
@@ -2036,7 +2030,7 @@
         <v>0.5854166666666667</v>
       </c>
       <c r="F43" s="3">
-        <f>E43-D43</f>
+        <f t="shared" si="1"/>
         <v>2.2916666666666696E-2</v>
       </c>
       <c r="G43">
@@ -2052,7 +2046,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>23</v>
       </c>
@@ -2069,7 +2063,7 @@
         <v>0.6020833333333333</v>
       </c>
       <c r="F44" s="3">
-        <f>E44-D44</f>
+        <f t="shared" si="1"/>
         <v>1.3194444444444398E-2</v>
       </c>
       <c r="G44">
@@ -2085,7 +2079,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>23</v>
       </c>
@@ -2102,7 +2096,7 @@
         <v>0.625</v>
       </c>
       <c r="F45" s="3">
-        <f>E45-D45</f>
+        <f t="shared" si="1"/>
         <v>1.9444444444444486E-2</v>
       </c>
       <c r="G45">
@@ -2118,7 +2112,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>24</v>
       </c>
@@ -2135,7 +2129,7 @@
         <v>0.56597222222222221</v>
       </c>
       <c r="F46" s="3">
-        <f>E46-D46</f>
+        <f t="shared" si="1"/>
         <v>1.2499999999999956E-2</v>
       </c>
       <c r="G46">
@@ -2151,7 +2145,7 @@
         <v>77.5</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>24</v>
       </c>
@@ -2168,7 +2162,7 @@
         <v>0.59861111111111109</v>
       </c>
       <c r="F47" s="3">
-        <f>E47-D47</f>
+        <f t="shared" si="1"/>
         <v>2.777777777777779E-2</v>
       </c>
       <c r="G47">
@@ -2184,7 +2178,7 @@
         <v>92.5</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>24</v>
       </c>
@@ -2201,7 +2195,7 @@
         <v>0.62638888888888888</v>
       </c>
       <c r="F48" s="3">
-        <f>E48-D48</f>
+        <f t="shared" si="1"/>
         <v>2.0138888888888928E-2</v>
       </c>
       <c r="G48">
@@ -2217,7 +2211,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>24</v>
       </c>
@@ -2234,7 +2228,7 @@
         <v>0.65138888888888891</v>
       </c>
       <c r="F49" s="3">
-        <f>E49-D49</f>
+        <f t="shared" si="1"/>
         <v>2.1527777777777812E-2</v>
       </c>
       <c r="G49">
@@ -2250,7 +2244,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>25</v>
       </c>
@@ -2267,7 +2261,7 @@
         <v>0.57777777777777772</v>
       </c>
       <c r="F50" s="3">
-        <f>E50-D50</f>
+        <f t="shared" si="1"/>
         <v>2.2222222222222143E-2</v>
       </c>
       <c r="G50">
@@ -2283,7 +2277,7 @@
         <v>97.5</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>25</v>
       </c>
@@ -2300,7 +2294,7 @@
         <v>0.6</v>
       </c>
       <c r="F51" s="3">
-        <f>E51-D51</f>
+        <f t="shared" si="1"/>
         <v>1.8749999999999933E-2</v>
       </c>
       <c r="G51">
@@ -2316,7 +2310,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>25</v>
       </c>
@@ -2333,7 +2327,7 @@
         <v>0.61041666666666672</v>
       </c>
       <c r="F52" s="3">
-        <f>E52-D52</f>
+        <f t="shared" si="1"/>
         <v>8.3333333333334147E-3</v>
       </c>
       <c r="G52">
@@ -2349,7 +2343,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>25</v>
       </c>
@@ -2366,7 +2360,7 @@
         <v>0.6166666666666667</v>
       </c>
       <c r="F53" s="3">
-        <f>E53-D53</f>
+        <f t="shared" si="1"/>
         <v>4.8611111111110938E-3</v>
       </c>
       <c r="G53">
@@ -2382,7 +2376,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>26</v>
       </c>
@@ -2399,7 +2393,7 @@
         <v>0.56666666666666665</v>
       </c>
       <c r="F54" s="3">
-        <f>E54-D54</f>
+        <f t="shared" si="1"/>
         <v>9.7222222222221877E-3</v>
       </c>
       <c r="G54">
@@ -2415,7 +2409,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>26</v>
       </c>
@@ -2432,7 +2426,7 @@
         <v>0.5708333333333333</v>
       </c>
       <c r="F55" s="3">
-        <f>E55-D55</f>
+        <f t="shared" si="1"/>
         <v>4.1666666666666519E-3</v>
       </c>
       <c r="G55">
@@ -2448,7 +2442,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>26</v>
       </c>
@@ -2465,7 +2459,7 @@
         <v>0.6</v>
       </c>
       <c r="F56" s="3">
-        <f>E56-D56</f>
+        <f t="shared" si="1"/>
         <v>2.8472222222222232E-2</v>
       </c>
       <c r="G56">
@@ -2481,7 +2475,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>26</v>
       </c>
@@ -2498,7 +2492,7 @@
         <v>0.62986111111111109</v>
       </c>
       <c r="F57" s="3">
-        <f>E57-D57</f>
+        <f t="shared" si="1"/>
         <v>2.9861111111111116E-2</v>
       </c>
       <c r="G57">
@@ -2514,7 +2508,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>27</v>
       </c>
@@ -2531,7 +2525,7 @@
         <v>0.59791666666666665</v>
       </c>
       <c r="F58" s="3">
-        <f>E58-D58</f>
+        <f t="shared" si="1"/>
         <v>4.2361111111111072E-2</v>
       </c>
       <c r="G58">
@@ -2547,7 +2541,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>27</v>
       </c>
@@ -2564,7 +2558,7 @@
         <v>0.60972222222222228</v>
       </c>
       <c r="F59" s="3">
-        <f>E59-D59</f>
+        <f t="shared" si="1"/>
         <v>1.1111111111111183E-2</v>
       </c>
       <c r="G59">
@@ -2580,7 +2574,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>27</v>
       </c>
@@ -2597,7 +2591,7 @@
         <v>0.625</v>
       </c>
       <c r="F60" s="3">
-        <f>E60-D60</f>
+        <f t="shared" si="1"/>
         <v>4.8611111111110938E-3</v>
       </c>
       <c r="G60">
@@ -2613,7 +2607,7 @@
         <v>77.5</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>27</v>
       </c>
@@ -2630,7 +2624,7 @@
         <v>0.65138888888888891</v>
       </c>
       <c r="F61" s="3">
-        <f>E61-D61</f>
+        <f t="shared" si="1"/>
         <v>2.2222222222222254E-2</v>
       </c>
       <c r="G61">
@@ -2646,7 +2640,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>28</v>
       </c>
@@ -2663,7 +2657,7 @@
         <v>0.59652777777777777</v>
       </c>
       <c r="F62" s="3">
-        <f>E62-D62</f>
+        <f t="shared" si="1"/>
         <v>4.3749999999999956E-2</v>
       </c>
       <c r="G62">
@@ -2679,7 +2673,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>28</v>
       </c>
@@ -2696,7 +2690,7 @@
         <v>0.65277777777777779</v>
       </c>
       <c r="F63" s="3">
-        <f>E63-D63</f>
+        <f t="shared" si="1"/>
         <v>2.2916666666666696E-2</v>
       </c>
       <c r="G63">
@@ -2712,7 +2706,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>28</v>
       </c>
@@ -2729,7 +2723,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="F64" s="3">
-        <f>E64-D64</f>
+        <f t="shared" si="1"/>
         <v>1.3194444444444398E-2</v>
       </c>
       <c r="G64">
@@ -2745,7 +2739,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>28</v>
       </c>
@@ -2762,7 +2756,7 @@
         <v>0.625</v>
       </c>
       <c r="F65" s="3">
-        <f>E65-D65</f>
+        <f t="shared" si="1"/>
         <v>2.777777777777779E-2</v>
       </c>
       <c r="G65">
@@ -2778,7 +2772,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>29</v>
       </c>
@@ -2795,7 +2789,7 @@
         <v>0.56736111111111109</v>
       </c>
       <c r="F66" s="3">
-        <f>E66-D66</f>
+        <f t="shared" ref="F66:F97" si="2">E66-D66</f>
         <v>1.1805555555555514E-2</v>
       </c>
       <c r="G66">
@@ -2811,7 +2805,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>29</v>
       </c>
@@ -2828,7 +2822,7 @@
         <v>0.58194444444444449</v>
       </c>
       <c r="F67" s="3">
-        <f>E67-D67</f>
+        <f t="shared" si="2"/>
         <v>9.0277777777778567E-3</v>
       </c>
       <c r="G67">
@@ -2844,7 +2838,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>29</v>
       </c>
@@ -2861,7 +2855,7 @@
         <v>0.59722222222222221</v>
       </c>
       <c r="F68" s="3">
-        <f>E68-D68</f>
+        <f t="shared" si="2"/>
         <v>1.041666666666663E-2</v>
       </c>
       <c r="G68">
@@ -2877,7 +2871,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>29</v>
       </c>
@@ -2894,7 +2888,7 @@
         <v>0.61597222222222225</v>
       </c>
       <c r="F69" s="3">
-        <f>E69-D69</f>
+        <f t="shared" si="2"/>
         <v>1.1805555555555625E-2</v>
       </c>
       <c r="G69">
@@ -2910,7 +2904,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>30</v>
       </c>
@@ -2927,7 +2921,7 @@
         <v>0.57361111111111107</v>
       </c>
       <c r="F70" s="3">
-        <f>E70-D70</f>
+        <f t="shared" si="2"/>
         <v>2.0138888888888817E-2</v>
       </c>
       <c r="G70">
@@ -2943,7 +2937,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>30</v>
       </c>
@@ -2960,7 +2954,7 @@
         <v>0.59444444444444444</v>
       </c>
       <c r="F71" s="3">
-        <f>E71-D71</f>
+        <f t="shared" si="2"/>
         <v>1.388888888888884E-2</v>
       </c>
       <c r="G71">
@@ -2976,7 +2970,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>30</v>
       </c>
@@ -2993,7 +2987,7 @@
         <v>0.64930555555555558</v>
       </c>
       <c r="F72" s="3">
-        <f>E72-D72</f>
+        <f t="shared" si="2"/>
         <v>1.6666666666666718E-2</v>
       </c>
       <c r="G72">
@@ -3009,7 +3003,7 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>30</v>
       </c>
@@ -3026,7 +3020,7 @@
         <v>0.63124999999999998</v>
       </c>
       <c r="F73" s="3">
-        <f>E73-D73</f>
+        <f t="shared" si="2"/>
         <v>2.9166666666666674E-2</v>
       </c>
       <c r="G73">
@@ -3042,7 +3036,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>31</v>
       </c>
@@ -3059,7 +3053,7 @@
         <v>0.59375</v>
       </c>
       <c r="F74" s="3">
-        <f>E74-D74</f>
+        <f t="shared" si="2"/>
         <v>2.430555555555558E-2</v>
       </c>
       <c r="G74">
@@ -3075,7 +3069,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>31</v>
       </c>
@@ -3092,7 +3086,7 @@
         <v>0.65902777777777777</v>
       </c>
       <c r="F75" s="3">
-        <f>E75-D75</f>
+        <f t="shared" si="2"/>
         <v>6.25E-2</v>
       </c>
       <c r="G75">
@@ -3108,7 +3102,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>31</v>
       </c>
@@ -3125,7 +3119,7 @@
         <v>0.68055555555555558</v>
       </c>
       <c r="F76" s="3">
-        <f>E76-D76</f>
+        <f t="shared" si="2"/>
         <v>1.6666666666666718E-2</v>
       </c>
       <c r="G76">
@@ -3141,7 +3135,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>31</v>
       </c>
@@ -3158,7 +3152,7 @@
         <v>0.70277777777777772</v>
       </c>
       <c r="F77" s="3">
-        <f>E77-D77</f>
+        <f t="shared" si="2"/>
         <v>1.5972222222222165E-2</v>
       </c>
       <c r="G77">
@@ -3174,7 +3168,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>32</v>
       </c>
@@ -3191,7 +3185,7 @@
         <v>0.4201388888888889</v>
       </c>
       <c r="F78" s="3">
-        <f>E78-D78</f>
+        <f t="shared" si="2"/>
         <v>4.6527777777777779E-2</v>
       </c>
       <c r="G78">
@@ -3207,7 +3201,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>32</v>
       </c>
@@ -3224,7 +3218,7 @@
         <v>0.44166666666666665</v>
       </c>
       <c r="F79" s="3">
-        <f>E79-D79</f>
+        <f t="shared" si="2"/>
         <v>1.4583333333333337E-2</v>
       </c>
       <c r="G79">
@@ -3240,7 +3234,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>32</v>
       </c>
@@ -3257,7 +3251,7 @@
         <v>0.49375000000000002</v>
       </c>
       <c r="F80" s="3">
-        <f>E80-D80</f>
+        <f t="shared" si="2"/>
         <v>3.8888888888888917E-2</v>
       </c>
       <c r="G80">
@@ -3273,7 +3267,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>32</v>
       </c>
@@ -3290,7 +3284,7 @@
         <v>0.51875000000000004</v>
       </c>
       <c r="F81" s="3">
-        <f>E81-D81</f>
+        <f t="shared" si="2"/>
         <v>2.083333333333337E-2</v>
       </c>
       <c r="G81">
@@ -3306,7 +3300,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>34</v>
       </c>
@@ -3323,7 +3317,7 @@
         <v>0.38819444444444445</v>
       </c>
       <c r="F82" s="3">
-        <f>E82-D82</f>
+        <f t="shared" si="2"/>
         <v>1.3194444444444453E-2</v>
       </c>
       <c r="G82">
@@ -3339,7 +3333,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>34</v>
       </c>
@@ -3356,7 +3350,7 @@
         <v>0.40416666666666667</v>
       </c>
       <c r="F83" s="3">
-        <f>E83-D83</f>
+        <f t="shared" si="2"/>
         <v>1.5972222222222221E-2</v>
       </c>
       <c r="G83">
@@ -3372,7 +3366,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>34</v>
       </c>
@@ -3389,7 +3383,7 @@
         <v>0.42152777777777778</v>
       </c>
       <c r="F84" s="3">
-        <f>E84-D84</f>
+        <f t="shared" si="2"/>
         <v>1.5972222222222221E-2</v>
       </c>
       <c r="G84">
@@ -3405,7 +3399,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>34</v>
       </c>
@@ -3422,7 +3416,7 @@
         <v>0.45416666666666666</v>
       </c>
       <c r="F85" s="3">
-        <f>E85-D85</f>
+        <f t="shared" si="2"/>
         <v>2.9166666666666674E-2</v>
       </c>
       <c r="G85">
@@ -3438,7 +3432,7 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>35</v>
       </c>
@@ -3455,7 +3449,7 @@
         <v>0.41319444444444442</v>
       </c>
       <c r="F86" s="3">
-        <f>E86-D86</f>
+        <f t="shared" si="2"/>
         <v>3.6111111111111094E-2</v>
       </c>
       <c r="G86">
@@ -3471,7 +3465,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="87" spans="1:10">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>35</v>
       </c>
@@ -3488,7 +3482,7 @@
         <v>0.4375</v>
       </c>
       <c r="F87" s="3">
-        <f>E87-D87</f>
+        <f t="shared" si="2"/>
         <v>2.0833333333333315E-2</v>
       </c>
       <c r="G87">
@@ -3504,7 +3498,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="88" spans="1:10">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>35</v>
       </c>
@@ -3521,7 +3515,7 @@
         <v>0.47708333333333336</v>
       </c>
       <c r="F88" s="3">
-        <f>E88-D88</f>
+        <f t="shared" si="2"/>
         <v>3.4722222222222265E-2</v>
       </c>
       <c r="G88">
@@ -3537,7 +3531,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>35</v>
       </c>
@@ -3554,7 +3548,7 @@
         <v>0.54027777777777775</v>
       </c>
       <c r="F89" s="3">
-        <f>E89-D89</f>
+        <f t="shared" si="2"/>
         <v>5.6944444444444409E-2</v>
       </c>
       <c r="G89">
@@ -3570,7 +3564,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>36</v>
       </c>
@@ -3587,7 +3581,7 @@
         <v>0.44236111111111109</v>
       </c>
       <c r="F90" s="3">
-        <f>E90-D90</f>
+        <f t="shared" si="2"/>
         <v>5.6249999999999967E-2</v>
       </c>
       <c r="G90">
@@ -3603,7 +3597,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="91" spans="1:10">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>36</v>
       </c>
@@ -3620,7 +3614,7 @@
         <v>0.46388888888888891</v>
       </c>
       <c r="F91" s="3">
-        <f>E91-D91</f>
+        <f t="shared" si="2"/>
         <v>2.0138888888888928E-2</v>
       </c>
       <c r="G91">
@@ -3636,7 +3630,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>36</v>
       </c>
@@ -3653,7 +3647,7 @@
         <v>0.49513888888888891</v>
       </c>
       <c r="F92" s="3">
-        <f>E92-D92</f>
+        <f t="shared" si="2"/>
         <v>2.8472222222222232E-2</v>
       </c>
       <c r="G92">
@@ -3669,7 +3663,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>36</v>
       </c>
@@ -3686,7 +3680,7 @@
         <v>0.53819444444444442</v>
       </c>
       <c r="F93" s="3">
-        <f>E93-D93</f>
+        <f t="shared" si="2"/>
         <v>4.166666666666663E-2</v>
       </c>
       <c r="G93">
@@ -3702,7 +3696,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>37</v>
       </c>
@@ -3719,7 +3713,7 @@
         <v>0.43472222222222223</v>
       </c>
       <c r="F94" s="3">
-        <f>E94-D94</f>
+        <f t="shared" si="2"/>
         <v>4.5833333333333337E-2</v>
       </c>
       <c r="G94">
@@ -3735,7 +3729,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>37</v>
       </c>
@@ -3752,7 +3746,7 @@
         <v>0.47013888888888888</v>
       </c>
       <c r="F95" s="3">
-        <f>E95-D95</f>
+        <f t="shared" si="2"/>
         <v>2.2916666666666641E-2</v>
       </c>
       <c r="G95">
@@ -3768,7 +3762,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="96" spans="1:10">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>37</v>
       </c>
@@ -3785,7 +3779,7 @@
         <v>0.50486111111111109</v>
       </c>
       <c r="F96" s="3">
-        <f>E96-D96</f>
+        <f t="shared" si="2"/>
         <v>2.8472222222222232E-2</v>
       </c>
       <c r="G96">
@@ -3801,7 +3795,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>37</v>
       </c>
@@ -3818,7 +3812,7 @@
         <v>0.52569444444444446</v>
       </c>
       <c r="F97" s="3">
-        <f>E97-D97</f>
+        <f t="shared" si="2"/>
         <v>1.3888888888888951E-2</v>
       </c>
       <c r="G97">
@@ -3834,7 +3828,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>38</v>
       </c>
@@ -3851,7 +3845,7 @@
         <v>0.4152777777777778</v>
       </c>
       <c r="F98" s="3">
-        <f>E98-D98</f>
+        <f t="shared" ref="F98:F129" si="3">E98-D98</f>
         <v>3.4722222222222265E-2</v>
       </c>
       <c r="G98">
@@ -3867,7 +3861,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>38</v>
       </c>
@@ -3884,7 +3878,7 @@
         <v>0.42916666666666664</v>
       </c>
       <c r="F99" s="3">
-        <f>E99-D99</f>
+        <f t="shared" si="3"/>
         <v>1.1805555555555514E-2</v>
       </c>
       <c r="G99">
@@ -3900,7 +3894,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>38</v>
       </c>
@@ -3917,7 +3911,7 @@
         <v>0.47708333333333336</v>
       </c>
       <c r="F100" s="3">
-        <f>E100-D100</f>
+        <f t="shared" si="3"/>
         <v>4.7916666666666718E-2</v>
       </c>
       <c r="G100">
@@ -3933,7 +3927,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>38</v>
       </c>
@@ -3950,7 +3944,7 @@
         <v>0.49861111111111112</v>
       </c>
       <c r="F101" s="3">
-        <f>E101-D101</f>
+        <f t="shared" si="3"/>
         <v>2.0138888888888873E-2</v>
       </c>
       <c r="G101">
@@ -3966,7 +3960,7 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>39</v>
       </c>
@@ -3983,7 +3977,7 @@
         <v>0.43194444444444446</v>
       </c>
       <c r="F102" s="3">
-        <f>E102-D102</f>
+        <f t="shared" si="3"/>
         <v>4.5833333333333337E-2</v>
       </c>
       <c r="G102">
@@ -3999,7 +3993,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="103" spans="1:10">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>39</v>
       </c>
@@ -4016,7 +4010,7 @@
         <v>0.45624999999999999</v>
       </c>
       <c r="F103" s="3">
-        <f>E103-D103</f>
+        <f t="shared" si="3"/>
         <v>2.3611111111111083E-2</v>
       </c>
       <c r="G103">
@@ -4032,7 +4026,7 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>39</v>
       </c>
@@ -4049,7 +4043,7 @@
         <v>0.51458333333333328</v>
       </c>
       <c r="F104" s="3">
-        <f>E104-D104</f>
+        <f t="shared" si="3"/>
         <v>4.7222222222222165E-2</v>
       </c>
       <c r="G104">
@@ -4065,7 +4059,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>39</v>
       </c>
@@ -4082,7 +4076,7 @@
         <v>0.54236111111111107</v>
       </c>
       <c r="F105" s="3">
-        <f>E105-D105</f>
+        <f t="shared" si="3"/>
         <v>2.1527777777777701E-2</v>
       </c>
       <c r="G105">
@@ -4098,7 +4092,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>40</v>
       </c>
@@ -4115,7 +4109,7 @@
         <v>0.40972222222222221</v>
       </c>
       <c r="F106" s="3">
-        <f>E106-D106</f>
+        <f t="shared" si="3"/>
         <v>2.0833333333333315E-2</v>
       </c>
       <c r="G106">
@@ -4131,7 +4125,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>40</v>
       </c>
@@ -4148,7 +4142,7 @@
         <v>0.44861111111111113</v>
       </c>
       <c r="F107" s="3">
-        <f>E107-D107</f>
+        <f t="shared" si="3"/>
         <v>6.9444444444444753E-3</v>
       </c>
       <c r="G107">
@@ -4164,7 +4158,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>40</v>
       </c>
@@ -4181,7 +4175,7 @@
         <v>0.41319444444444442</v>
       </c>
       <c r="F108" s="3">
-        <f>E108-D108</f>
+        <f t="shared" si="3"/>
         <v>6.9444444444444198E-4</v>
       </c>
       <c r="G108">
@@ -4197,7 +4191,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="109" spans="1:10">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>40</v>
       </c>
@@ -4214,7 +4208,7 @@
         <v>0.44166666666666665</v>
       </c>
       <c r="F109" s="3">
-        <f>E109-D109</f>
+        <f t="shared" si="3"/>
         <v>2.0833333333333315E-2</v>
       </c>
       <c r="G109">
@@ -4230,7 +4224,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>41</v>
       </c>
@@ -4247,7 +4241,7 @@
         <v>0.43402777777777779</v>
       </c>
       <c r="F110" s="3">
-        <f>E110-D110</f>
+        <f t="shared" si="3"/>
         <v>4.8611111111111105E-2</v>
       </c>
       <c r="G110">
@@ -4263,7 +4257,7 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="111" spans="1:10">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>41</v>
       </c>
@@ -4280,7 +4274,7 @@
         <v>0.46666666666666667</v>
       </c>
       <c r="F111" s="3">
-        <f>E111-D111</f>
+        <f t="shared" si="3"/>
         <v>2.5694444444444464E-2</v>
       </c>
       <c r="G111">
@@ -4296,7 +4290,7 @@
         <v>77.5</v>
       </c>
     </row>
-    <row r="112" spans="1:10">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>41</v>
       </c>
@@ -4313,7 +4307,7 @@
         <v>0.50694444444444442</v>
       </c>
       <c r="F112" s="3">
-        <f>E112-D112</f>
+        <f t="shared" si="3"/>
         <v>2.7083333333333293E-2</v>
       </c>
       <c r="G112">
@@ -4329,7 +4323,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="113" spans="1:10">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>41</v>
       </c>
@@ -4346,7 +4340,7 @@
         <v>0.47986111111111113</v>
       </c>
       <c r="F113" s="3">
-        <f>E113-D113</f>
+        <f t="shared" si="3"/>
         <v>1.3194444444444453E-2</v>
       </c>
       <c r="G113">
@@ -4362,7 +4356,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="114" spans="1:10">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>42</v>
       </c>
@@ -4379,7 +4373,7 @@
         <v>0.41180555555555554</v>
       </c>
       <c r="F114" s="3">
-        <f>E114-D114</f>
+        <f t="shared" si="3"/>
         <v>2.8472222222222177E-2</v>
       </c>
       <c r="G114">
@@ -4395,7 +4389,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="115" spans="1:10">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>42</v>
       </c>
@@ -4412,7 +4406,7 @@
         <v>0.4513888888888889</v>
       </c>
       <c r="F115" s="3">
-        <f>E115-D115</f>
+        <f t="shared" si="3"/>
         <v>2.0833333333333315E-2</v>
       </c>
       <c r="G115">
@@ -4428,7 +4422,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="116" spans="1:10">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>42</v>
       </c>
@@ -4445,7 +4439,7 @@
         <v>0.54166666666666663</v>
       </c>
       <c r="F116" s="3">
-        <f>E116-D116</f>
+        <f t="shared" si="3"/>
         <v>6.944444444444442E-2</v>
       </c>
       <c r="G116">
@@ -4461,7 +4455,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>42</v>
       </c>
@@ -4478,7 +4472,7 @@
         <v>0.42708333333333331</v>
       </c>
       <c r="F117" s="3">
-        <f>E117-D117</f>
+        <f t="shared" si="3"/>
         <v>1.3888888888888895E-2</v>
       </c>
       <c r="G117">
@@ -4494,7 +4488,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="118" spans="1:10">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>43</v>
       </c>
@@ -4511,7 +4505,7 @@
         <v>0.40972222222222221</v>
       </c>
       <c r="F118" s="3">
-        <f>E118-D118</f>
+        <f t="shared" si="3"/>
         <v>2.0833333333333315E-2</v>
       </c>
       <c r="G118">
@@ -4527,7 +4521,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="119" spans="1:10">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>43</v>
       </c>
@@ -4544,7 +4538,7 @@
         <v>0.43888888888888888</v>
       </c>
       <c r="F119" s="3">
-        <f>E119-D119</f>
+        <f t="shared" si="3"/>
         <v>2.2222222222222199E-2</v>
       </c>
       <c r="G119">
@@ -4560,7 +4554,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="120" spans="1:10">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>43</v>
       </c>
@@ -4577,7 +4571,7 @@
         <v>0.46041666666666664</v>
       </c>
       <c r="F120" s="3">
-        <f>E120-D120</f>
+        <f t="shared" si="3"/>
         <v>1.9444444444444431E-2</v>
       </c>
       <c r="G120">
@@ -4593,7 +4587,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="121" spans="1:10">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>43</v>
       </c>
@@ -4610,7 +4604,7 @@
         <v>0.50624999999999998</v>
       </c>
       <c r="F121" s="3">
-        <f>E121-D121</f>
+        <f t="shared" si="3"/>
         <v>4.166666666666663E-2</v>
       </c>
       <c r="G121">
@@ -4626,7 +4620,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="122" spans="1:10">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>44</v>
       </c>
@@ -4643,7 +4637,7 @@
         <v>0.44374999999999998</v>
       </c>
       <c r="F122" s="3">
-        <f>E122-D122</f>
+        <f t="shared" si="3"/>
         <v>6.3888888888888884E-2</v>
       </c>
       <c r="G122">
@@ -4659,7 +4653,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="123" spans="1:10">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>44</v>
       </c>
@@ -4676,7 +4670,7 @@
         <v>0.46041666666666664</v>
       </c>
       <c r="F123" s="3">
-        <f>E123-D123</f>
+        <f t="shared" si="3"/>
         <v>1.3194444444444398E-2</v>
       </c>
       <c r="G123">
@@ -4692,7 +4686,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="124" spans="1:10">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>44</v>
       </c>
@@ -4709,7 +4703,7 @@
         <v>0.50347222222222221</v>
       </c>
       <c r="F124" s="3">
-        <f>E124-D124</f>
+        <f t="shared" si="3"/>
         <v>3.3333333333333326E-2</v>
       </c>
       <c r="G124">
@@ -4725,7 +4719,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="125" spans="1:10">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>44</v>
       </c>
@@ -4742,7 +4736,7 @@
         <v>0.53472222222222221</v>
       </c>
       <c r="F125" s="3">
-        <f>E125-D125</f>
+        <f t="shared" si="3"/>
         <v>2.083333333333337E-2</v>
       </c>
       <c r="G125">
@@ -4758,7 +4752,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="126" spans="1:10">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>45</v>
       </c>
@@ -4775,7 +4769,7 @@
         <v>0.40555555555555556</v>
       </c>
       <c r="F126" s="3">
-        <f>E126-D126</f>
+        <f t="shared" si="3"/>
         <v>1.5277777777777779E-2</v>
       </c>
       <c r="G126">
@@ -4791,7 +4785,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="127" spans="1:10">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>45</v>
       </c>
@@ -4808,7 +4802,7 @@
         <v>0.42638888888888887</v>
       </c>
       <c r="F127" s="3">
-        <f>E127-D127</f>
+        <f t="shared" si="3"/>
         <v>1.5277777777777779E-2</v>
       </c>
       <c r="G127">
@@ -4824,7 +4818,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="128" spans="1:10">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>45</v>
       </c>
@@ -4841,7 +4835,7 @@
         <v>0.45347222222222222</v>
       </c>
       <c r="F128" s="3">
-        <f>E128-D128</f>
+        <f t="shared" si="3"/>
         <v>2.430555555555558E-2</v>
       </c>
       <c r="G128">
@@ -4857,7 +4851,7 @@
         <v>47.5</v>
       </c>
     </row>
-    <row r="129" spans="1:10">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>45</v>
       </c>
@@ -4874,7 +4868,7 @@
         <v>0.49930555555555556</v>
       </c>
       <c r="F129" s="3">
-        <f>E129-D129</f>
+        <f t="shared" si="3"/>
         <v>4.5833333333333337E-2</v>
       </c>
       <c r="G129">
@@ -4890,7 +4884,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="130" spans="1:10">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>46</v>
       </c>
@@ -4907,7 +4901,7 @@
         <v>0.42291666666666666</v>
       </c>
       <c r="F130" s="3">
-        <f>E130-D130</f>
+        <f t="shared" ref="F130:F149" si="4">E130-D130</f>
         <v>2.3611111111111083E-2</v>
       </c>
       <c r="G130">
@@ -4923,7 +4917,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="131" spans="1:10">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>46</v>
       </c>
@@ -4940,7 +4934,7 @@
         <v>0.43541666666666667</v>
       </c>
       <c r="F131" s="3">
-        <f>E131-D131</f>
+        <f t="shared" si="4"/>
         <v>1.1805555555555569E-2</v>
       </c>
       <c r="G131">
@@ -4956,7 +4950,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="132" spans="1:10">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>46</v>
       </c>
@@ -4973,7 +4967,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="F132" s="3">
-        <f>E132-D132</f>
+        <f t="shared" si="4"/>
         <v>1.7361111111111105E-2</v>
       </c>
       <c r="G132">
@@ -4989,7 +4983,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="133" spans="1:10">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>46</v>
       </c>
@@ -5006,7 +5000,7 @@
         <v>0.50416666666666665</v>
       </c>
       <c r="F133" s="3">
-        <f>E133-D133</f>
+        <f t="shared" si="4"/>
         <v>4.166666666666663E-2</v>
       </c>
       <c r="G133">
@@ -5022,7 +5016,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="134" spans="1:10">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>47</v>
       </c>
@@ -5039,7 +5033,7 @@
         <v>0.40763888888888888</v>
       </c>
       <c r="F134" s="3">
-        <f>E134-D134</f>
+        <f t="shared" si="4"/>
         <v>1.8749999999999989E-2</v>
       </c>
       <c r="G134">
@@ -5055,7 +5049,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="12.6" customHeight="1">
+    <row r="135" spans="1:10" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>47</v>
       </c>
@@ -5072,7 +5066,7 @@
         <v>0.42916666666666664</v>
       </c>
       <c r="F135" s="3">
-        <f>E135-D135</f>
+        <f t="shared" si="4"/>
         <v>2.2916666666666641E-2</v>
       </c>
       <c r="G135">
@@ -5088,7 +5082,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="136" spans="1:10">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>47</v>
       </c>
@@ -5105,7 +5099,7 @@
         <v>0.4513888888888889</v>
       </c>
       <c r="F136" s="3">
-        <f>E136-D136</f>
+        <f t="shared" si="4"/>
         <v>1.9444444444444431E-2</v>
       </c>
       <c r="G136">
@@ -5121,7 +5115,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="137" spans="1:10">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>47</v>
       </c>
@@ -5138,7 +5132,7 @@
         <v>0.47569444444444442</v>
       </c>
       <c r="F137" s="3">
-        <f>E137-D137</f>
+        <f t="shared" si="4"/>
         <v>1.7361111111111105E-2</v>
       </c>
       <c r="G137">
@@ -5154,7 +5148,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="138" spans="1:10">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>48</v>
       </c>
@@ -5171,7 +5165,7 @@
         <v>0.41319444444444442</v>
       </c>
       <c r="F138" s="3">
-        <f>E138-D138</f>
+        <f t="shared" si="4"/>
         <v>2.2916666666666641E-2</v>
       </c>
       <c r="G138">
@@ -5187,7 +5181,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="139" spans="1:10">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>48</v>
       </c>
@@ -5204,7 +5198,7 @@
         <v>0.44166666666666665</v>
       </c>
       <c r="F139" s="3">
-        <f>E139-D139</f>
+        <f t="shared" si="4"/>
         <v>2.4305555555555525E-2</v>
       </c>
       <c r="G139">
@@ -5220,7 +5214,7 @@
         <v>97.5</v>
       </c>
     </row>
-    <row r="140" spans="1:10">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>48</v>
       </c>
@@ -5237,7 +5231,7 @@
         <v>0.46041666666666664</v>
       </c>
       <c r="F140" s="3">
-        <f>E140-D140</f>
+        <f t="shared" si="4"/>
         <v>1.8749999999999989E-2</v>
       </c>
       <c r="G140">
@@ -5253,7 +5247,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="141" spans="1:10">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>48</v>
       </c>
@@ -5270,7 +5264,7 @@
         <v>0.55138888888888893</v>
       </c>
       <c r="F141" s="3">
-        <f>E141-D141</f>
+        <f t="shared" si="4"/>
         <v>8.2638888888888928E-2</v>
       </c>
       <c r="G141">
@@ -5286,7 +5280,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="142" spans="1:10">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>49</v>
       </c>
@@ -5303,7 +5297,7 @@
         <v>0.40694444444444444</v>
       </c>
       <c r="F142" s="3">
-        <f>E142-D142</f>
+        <f t="shared" si="4"/>
         <v>1.9444444444444431E-2</v>
       </c>
       <c r="G142">
@@ -5319,7 +5313,7 @@
         <v>77.5</v>
       </c>
     </row>
-    <row r="143" spans="1:10">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>49</v>
       </c>
@@ -5336,7 +5330,7 @@
         <v>0.41875000000000001</v>
       </c>
       <c r="F143" s="3">
-        <f>E143-D143</f>
+        <f t="shared" si="4"/>
         <v>8.3333333333333592E-3</v>
       </c>
       <c r="G143">
@@ -5352,7 +5346,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="144" spans="1:10">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>49</v>
       </c>
@@ -5369,7 +5363,7 @@
         <v>0.47152777777777777</v>
       </c>
       <c r="F144" s="3">
-        <f>E144-D144</f>
+        <f t="shared" si="4"/>
         <v>1.6666666666666663E-2</v>
       </c>
       <c r="G144">
@@ -5385,7 +5379,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="145" spans="1:10">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>49</v>
       </c>
@@ -5402,7 +5396,7 @@
         <v>0.5</v>
       </c>
       <c r="F145" s="3">
-        <f>E145-D145</f>
+        <f t="shared" si="4"/>
         <v>2.0833333333333315E-2</v>
       </c>
       <c r="G145">
@@ -5418,7 +5412,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="146" spans="1:10">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>50</v>
       </c>
@@ -5426,20 +5420,20 @@
         <v>1</v>
       </c>
       <c r="C146" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D146" s="2">
-        <v>0.43680555555555556</v>
+        <v>0.40277777777777779</v>
       </c>
       <c r="E146" s="2">
-        <v>0.47013888888888888</v>
+        <v>0.4375</v>
       </c>
       <c r="F146" s="3">
-        <f>E146-D146</f>
-        <v>3.3333333333333326E-2</v>
+        <f t="shared" si="4"/>
+        <v>3.472222222222221E-2</v>
       </c>
       <c r="G146">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H146" t="s">
         <v>33</v>
@@ -5447,8 +5441,11 @@
       <c r="I146">
         <v>4</v>
       </c>
-    </row>
-    <row r="147" spans="1:10">
+      <c r="J146">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>50</v>
       </c>
@@ -5456,20 +5453,20 @@
         <v>2</v>
       </c>
       <c r="C147" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D147" s="2">
-        <v>0.47499999999999998</v>
+        <v>0.44791666666666669</v>
       </c>
       <c r="E147" s="2">
-        <v>0.48055555555555557</v>
+        <v>0.45902777777777776</v>
       </c>
       <c r="F147" s="3">
-        <f>E147-D147</f>
-        <v>5.5555555555555913E-3</v>
+        <f t="shared" si="4"/>
+        <v>1.1111111111111072E-2</v>
       </c>
       <c r="G147">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H147" t="s">
         <v>33</v>
@@ -5481,7 +5478,7 @@
         <v>77.5</v>
       </c>
     </row>
-    <row r="148" spans="1:10">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>50</v>
       </c>
@@ -5492,17 +5489,17 @@
         <v>11</v>
       </c>
       <c r="D148" s="2">
-        <v>0.48194444444444445</v>
+        <v>0.46180555555555558</v>
       </c>
       <c r="E148" s="2">
-        <v>0.49930555555555556</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="F148" s="3">
-        <f>E148-D148</f>
+        <f t="shared" si="4"/>
         <v>1.7361111111111105E-2</v>
       </c>
       <c r="G148">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H148" t="s">
         <v>33</v>
@@ -5510,8 +5507,11 @@
       <c r="I148">
         <v>4</v>
       </c>
-    </row>
-    <row r="149" spans="1:10">
+      <c r="J148">
+        <v>72.5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>50</v>
       </c>
@@ -5522,17 +5522,17 @@
         <v>13</v>
       </c>
       <c r="D149" s="2">
-        <v>0.50347222222222221</v>
+        <v>0.4826388888888889</v>
       </c>
       <c r="E149" s="2">
-        <v>0.54722222222222228</v>
+        <v>0.52916666666666667</v>
       </c>
       <c r="F149" s="3">
-        <f>E149-D149</f>
-        <v>4.3750000000000067E-2</v>
+        <f t="shared" si="4"/>
+        <v>4.6527777777777779E-2</v>
       </c>
       <c r="G149">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H149" t="s">
         <v>33</v>
@@ -5541,268 +5541,16 @@
         <v>4</v>
       </c>
       <c r="J149">
-        <v>72.5</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10">
-      <c r="A150" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B150">
-        <v>1</v>
-      </c>
-      <c r="C150" t="s">
-        <v>11</v>
-      </c>
-      <c r="D150" s="2">
-        <v>0.40069444444444446</v>
-      </c>
-      <c r="E150" s="2">
-        <v>0.42916666666666664</v>
-      </c>
-      <c r="F150" s="3">
-        <f>E150-D150</f>
-        <v>2.8472222222222177E-2</v>
-      </c>
-      <c r="G150">
-        <v>2</v>
-      </c>
-      <c r="H150" t="s">
-        <v>33</v>
-      </c>
-      <c r="I150">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10">
-      <c r="A151" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B151">
-        <v>2</v>
-      </c>
-      <c r="C151" t="s">
-        <v>13</v>
-      </c>
-      <c r="D151" s="2">
-        <v>0.42986111111111114</v>
-      </c>
-      <c r="E151" s="2">
-        <v>0.43680555555555556</v>
-      </c>
-      <c r="F151" s="3">
-        <f>E151-D151</f>
-        <v>6.9444444444444198E-3</v>
-      </c>
-      <c r="G151">
-        <v>2</v>
-      </c>
-      <c r="H151" t="s">
-        <v>33</v>
-      </c>
-      <c r="I151">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10">
-      <c r="A152" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B152">
-        <v>3</v>
-      </c>
-      <c r="C152" t="s">
-        <v>13</v>
-      </c>
-      <c r="D152" s="2">
-        <v>0.44444444444444442</v>
-      </c>
-      <c r="E152" s="2">
-        <v>0.45902777777777776</v>
-      </c>
-      <c r="F152" s="3">
-        <f>E152-D152</f>
-        <v>1.4583333333333337E-2</v>
-      </c>
-      <c r="G152">
-        <v>2</v>
-      </c>
-      <c r="H152" t="s">
-        <v>33</v>
-      </c>
-      <c r="I152">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10">
-      <c r="A153" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B153">
-        <v>4</v>
-      </c>
-      <c r="C153" t="s">
-        <v>11</v>
-      </c>
-      <c r="D153" s="2">
-        <v>0.46805555555555556</v>
-      </c>
-      <c r="E153" s="2">
-        <v>0.48680555555555555</v>
-      </c>
-      <c r="F153" s="3">
-        <f>E153-D153</f>
-        <v>1.8749999999999989E-2</v>
-      </c>
-      <c r="G153">
-        <v>2</v>
-      </c>
-      <c r="H153" t="s">
-        <v>33</v>
-      </c>
-      <c r="I153">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10">
-      <c r="A154" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B154">
-        <v>1</v>
-      </c>
-      <c r="C154" t="s">
-        <v>13</v>
-      </c>
-      <c r="D154" s="2">
-        <v>0.40277777777777779</v>
-      </c>
-      <c r="E154" s="2">
-        <v>0.4375</v>
-      </c>
-      <c r="F154" s="3">
-        <f>E154-D154</f>
-        <v>3.472222222222221E-2</v>
-      </c>
-      <c r="G154">
-        <v>3</v>
-      </c>
-      <c r="H154" t="s">
-        <v>33</v>
-      </c>
-      <c r="I154">
-        <v>4</v>
-      </c>
-      <c r="J154">
         <v>70</v>
       </c>
     </row>
-    <row r="155" spans="1:10">
-      <c r="A155" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B155">
-        <v>2</v>
-      </c>
-      <c r="C155" t="s">
-        <v>11</v>
-      </c>
-      <c r="D155" s="2">
-        <v>0.44791666666666669</v>
-      </c>
-      <c r="E155" s="2">
-        <v>0.45902777777777776</v>
-      </c>
-      <c r="F155" s="3">
-        <f>E155-D155</f>
-        <v>1.1111111111111072E-2</v>
-      </c>
-      <c r="G155">
-        <v>3</v>
-      </c>
-      <c r="H155" t="s">
-        <v>33</v>
-      </c>
-      <c r="I155">
-        <v>4</v>
-      </c>
-      <c r="J155">
-        <v>77.5</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10">
-      <c r="A156" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B156">
-        <v>3</v>
-      </c>
-      <c r="C156" t="s">
-        <v>11</v>
-      </c>
-      <c r="D156" s="2">
-        <v>0.46180555555555558</v>
-      </c>
-      <c r="E156" s="2">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="F156" s="3">
-        <f>E156-D156</f>
-        <v>1.7361111111111105E-2</v>
-      </c>
-      <c r="G156">
-        <v>3</v>
-      </c>
-      <c r="H156" t="s">
-        <v>33</v>
-      </c>
-      <c r="I156">
-        <v>4</v>
-      </c>
-      <c r="J156">
-        <v>72.5</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10">
-      <c r="A157" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B157">
-        <v>4</v>
-      </c>
-      <c r="C157" t="s">
-        <v>13</v>
-      </c>
-      <c r="D157" s="2">
-        <v>0.4826388888888889</v>
-      </c>
-      <c r="E157" s="2">
-        <v>0.52916666666666667</v>
-      </c>
-      <c r="F157" s="3">
-        <f>E157-D157</f>
-        <v>4.6527777777777779E-2</v>
-      </c>
-      <c r="G157">
-        <v>3</v>
-      </c>
-      <c r="H157" t="s">
-        <v>33</v>
-      </c>
-      <c r="I157">
-        <v>4</v>
-      </c>
-      <c r="J157">
-        <v>70</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:E157">
+  <conditionalFormatting sqref="D2:E149">
     <cfRule type="containsBlanks" dxfId="1" priority="2">
       <formula>LEN(TRIM(D2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1 I1:I157">
+  <conditionalFormatting sqref="J1 I1:I149">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>4</formula>
     </cfRule>
@@ -5812,6 +5560,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC5B977DC2C7674F82055B70C433A343" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0c8840f1fe80ef94076c2dfaa2109b2c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="aa19b363-da07-439e-ac90-05542eb97bc0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5b668aa7a088d7c26539b2f29176b798" ns2:_="">
     <xsd:import namespace="aa19b363-da07-439e-ac90-05542eb97bc0"/>
@@ -5949,12 +5703,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -5965,13 +5713,36 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2EBFC51-D298-4C6A-9B0D-3F57395AA488}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEDC47A0-6315-4416-986A-387898343C81}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEDC47A0-6315-4416-986A-387898343C81}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2EBFC51-D298-4C6A-9B0D-3F57395AA488}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="aa19b363-da07-439e-ac90-05542eb97bc0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40DC5519-4D91-4988-9A25-B91DB3698213}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40DC5519-4D91-4988-9A25-B91DB3698213}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>